--- a/artfynd/A 33409-2026 artfynd.xlsx
+++ b/artfynd/A 33409-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ58"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120846244</v>
+        <v>136933815</v>
       </c>
       <c r="B26" t="n">
-        <v>58114</v>
+        <v>58008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,37 +3139,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sandträsket, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>784470</v>
+        <v>784323</v>
       </c>
       <c r="R26" t="n">
-        <v>7349932</v>
+        <v>7350455</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3193,12 +3198,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3213,66 +3233,67 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120846244</t>
+          <t>https://artportalen.se/Sighting/136933815</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126381207</v>
+        <v>136933817</v>
       </c>
       <c r="B27" t="n">
-        <v>99035</v>
+        <v>58008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsket, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>784369</v>
+        <v>784190</v>
       </c>
       <c r="R27" t="n">
-        <v>7350109</v>
+        <v>7350329</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3299,12 +3320,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3319,66 +3355,67 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Kristoffersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Kristoffersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126381207</t>
+          <t>https://artportalen.se/Sighting/136933817</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126381211</v>
+        <v>136933818</v>
       </c>
       <c r="B28" t="n">
-        <v>99035</v>
+        <v>58008</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsket, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>784336</v>
+        <v>784220</v>
       </c>
       <c r="R28" t="n">
-        <v>7350140</v>
+        <v>7350314</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3405,12 +3442,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3425,49 +3477,49 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Kristoffersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Kristoffersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126381211</t>
+          <t>https://artportalen.se/Sighting/136933818</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120846243</v>
+        <v>120846244</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3477,10 +3529,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>784480</v>
+        <v>784470</v>
       </c>
       <c r="R29" t="n">
-        <v>7349944</v>
+        <v>7349932</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3538,54 +3590,59 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120846243</t>
+          <t>https://artportalen.se/Sighting/120846244</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120846272</v>
+        <v>136933819</v>
       </c>
       <c r="B30" t="n">
-        <v>99118</v>
+        <v>58169</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sandträsket, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>784454</v>
+        <v>784287</v>
       </c>
       <c r="R30" t="n">
-        <v>7349938</v>
+        <v>7350089</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3609,12 +3666,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3629,65 +3696,69 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120846272</t>
+          <t>https://artportalen.se/Sighting/136933819</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126284256</v>
+        <v>126381207</v>
       </c>
       <c r="B31" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sandträsk, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
         <v>784369</v>
       </c>
       <c r="R31" t="n">
-        <v>7350111</v>
+        <v>7350109</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3711,17 +3782,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>25 +15 rosetter  tre blomställningar</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3736,65 +3802,69 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Johan Kristoffersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Johan Kristoffersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126284256</t>
+          <t>https://artportalen.se/Sighting/126381207</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126284257</v>
+        <v>126381211</v>
       </c>
       <c r="B32" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sandträsk, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>784377</v>
+        <v>784336</v>
       </c>
       <c r="R32" t="n">
-        <v>7350105</v>
+        <v>7350140</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3818,17 +3888,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>8 rosetter</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3843,24 +3908,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Johan Kristoffersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Johan Kristoffersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126284257</t>
+          <t>https://artportalen.se/Sighting/126381211</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126284258</v>
+        <v>120846243</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -3891,17 +3956,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sandträsk, Nb</t>
+          <t>Sandträsket, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>784337</v>
+        <v>784480</v>
       </c>
       <c r="R33" t="n">
-        <v>7350108</v>
+        <v>7349944</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3925,17 +3990,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>15tal</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3950,24 +4010,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126284258</t>
+          <t>https://artportalen.se/Sighting/120846243</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126284259</v>
+        <v>120846272</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -3998,17 +4058,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sandträsk, Nb</t>
+          <t>Sandträsket, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>784521</v>
+        <v>784454</v>
       </c>
       <c r="R34" t="n">
-        <v>7349985</v>
+        <v>7349938</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4032,17 +4092,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>5 bladrosetter</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4057,24 +4112,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126284259</t>
+          <t>https://artportalen.se/Sighting/120846272</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126284260</v>
+        <v>126284256</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4109,10 +4164,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>784524</v>
+        <v>784369</v>
       </c>
       <c r="R35" t="n">
-        <v>7349959</v>
+        <v>7350111</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4149,7 +4204,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>13 bladrosetter</t>
+          <t>25 +15 rosetter  tre blomställningar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4175,13 +4230,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126284260</t>
+          <t>https://artportalen.se/Sighting/126284256</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126284261</v>
+        <v>126284257</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4216,10 +4271,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>784519</v>
+        <v>784377</v>
       </c>
       <c r="R36" t="n">
-        <v>7349967</v>
+        <v>7350105</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4256,7 +4311,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>15 tal bladrosetter</t>
+          <t>8 rosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4282,13 +4337,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126284261</t>
+          <t>https://artportalen.se/Sighting/126284257</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126284262</v>
+        <v>126284258</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4323,10 +4378,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>784466</v>
+        <v>784337</v>
       </c>
       <c r="R37" t="n">
-        <v>7349966</v>
+        <v>7350108</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4363,7 +4418,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>4 bladrosetter</t>
+          <t>15tal</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4389,13 +4444,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126284262</t>
+          <t>https://artportalen.se/Sighting/126284258</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126380916</v>
+        <v>126284259</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4426,17 +4481,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsk, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>784338</v>
+        <v>784521</v>
       </c>
       <c r="R38" t="n">
-        <v>7350142</v>
+        <v>7349985</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4460,12 +4515,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4480,24 +4540,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Kristoffersson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Kristoffersson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380916</t>
+          <t>https://artportalen.se/Sighting/126284259</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126380917</v>
+        <v>126284260</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -4528,17 +4588,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsk, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>784355</v>
+        <v>784524</v>
       </c>
       <c r="R39" t="n">
-        <v>7350119</v>
+        <v>7349959</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4562,12 +4622,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4582,24 +4647,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Kristoffersson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Kristoffersson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380917</t>
+          <t>https://artportalen.se/Sighting/126284260</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126380918</v>
+        <v>126284261</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -4630,17 +4695,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsk, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>784340</v>
+        <v>784519</v>
       </c>
       <c r="R40" t="n">
-        <v>7350120</v>
+        <v>7349967</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4664,12 +4729,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>15 tal bladrosetter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4684,24 +4754,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Kristoffersson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Kristoffersson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380918</t>
+          <t>https://artportalen.se/Sighting/126284261</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126380919</v>
+        <v>126284262</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -4732,17 +4802,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsk, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>784341</v>
+        <v>784466</v>
       </c>
       <c r="R41" t="n">
-        <v>7350108</v>
+        <v>7349966</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4766,12 +4836,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>4 bladrosetter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4786,24 +4861,24 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Kristoffersson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Kristoffersson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380919</t>
+          <t>https://artportalen.se/Sighting/126284262</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126380920</v>
+        <v>126380916</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -4838,10 +4913,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>784332</v>
+        <v>784338</v>
       </c>
       <c r="R42" t="n">
-        <v>7350094</v>
+        <v>7350142</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4899,13 +4974,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380920</t>
+          <t>https://artportalen.se/Sighting/126380916</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126380921</v>
+        <v>126380917</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -4940,10 +5015,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>784344</v>
+        <v>784355</v>
       </c>
       <c r="R43" t="n">
-        <v>7350056</v>
+        <v>7350119</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5001,13 +5076,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380921</t>
+          <t>https://artportalen.se/Sighting/126380917</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126380922</v>
+        <v>126380918</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5042,10 +5117,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>784350</v>
+        <v>784340</v>
       </c>
       <c r="R44" t="n">
-        <v>7350038</v>
+        <v>7350120</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5103,13 +5178,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380922</t>
+          <t>https://artportalen.se/Sighting/126380918</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126380923</v>
+        <v>126380919</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5144,10 +5219,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>784373</v>
+        <v>784341</v>
       </c>
       <c r="R45" t="n">
-        <v>7350015</v>
+        <v>7350108</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5205,13 +5280,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380923</t>
+          <t>https://artportalen.se/Sighting/126380919</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126380924</v>
+        <v>126380920</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5246,10 +5321,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>784377</v>
+        <v>784332</v>
       </c>
       <c r="R46" t="n">
-        <v>7350011</v>
+        <v>7350094</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5307,13 +5382,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380924</t>
+          <t>https://artportalen.se/Sighting/126380920</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126380925</v>
+        <v>126380921</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -5348,10 +5423,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>784410</v>
+        <v>784344</v>
       </c>
       <c r="R47" t="n">
-        <v>7349970</v>
+        <v>7350056</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5409,13 +5484,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380925</t>
+          <t>https://artportalen.se/Sighting/126380921</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126380926</v>
+        <v>126380922</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -5450,10 +5525,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>784408</v>
+        <v>784350</v>
       </c>
       <c r="R48" t="n">
-        <v>7349964</v>
+        <v>7350038</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5511,13 +5586,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380926</t>
+          <t>https://artportalen.se/Sighting/126380922</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126380927</v>
+        <v>126380923</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -5545,21 +5620,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>784455</v>
+        <v>784373</v>
       </c>
       <c r="R49" t="n">
-        <v>7349924</v>
+        <v>7350015</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5617,13 +5688,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380927</t>
+          <t>https://artportalen.se/Sighting/126380923</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126380928</v>
+        <v>126380924</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -5651,21 +5722,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>784450</v>
+        <v>784377</v>
       </c>
       <c r="R50" t="n">
-        <v>7349934</v>
+        <v>7350011</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5723,13 +5790,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380928</t>
+          <t>https://artportalen.se/Sighting/126380924</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126380929</v>
+        <v>126380925</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -5757,21 +5824,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>784458</v>
+        <v>784410</v>
       </c>
       <c r="R51" t="n">
-        <v>7349938</v>
+        <v>7349970</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5829,13 +5892,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380929</t>
+          <t>https://artportalen.se/Sighting/126380925</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126380930</v>
+        <v>126380926</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -5863,21 +5926,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784469</v>
+        <v>784408</v>
       </c>
       <c r="R52" t="n">
-        <v>7349942</v>
+        <v>7349964</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5935,13 +5994,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380930</t>
+          <t>https://artportalen.se/Sighting/126380926</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126380932</v>
+        <v>126380927</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -5971,7 +6030,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5980,10 +6039,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>784515</v>
+        <v>784455</v>
       </c>
       <c r="R53" t="n">
-        <v>7349962</v>
+        <v>7349924</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6041,13 +6100,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380932</t>
+          <t>https://artportalen.se/Sighting/126380927</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126380933</v>
+        <v>126380928</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6077,7 +6136,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6086,10 +6145,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>784515</v>
+        <v>784450</v>
       </c>
       <c r="R54" t="n">
-        <v>7350041</v>
+        <v>7349934</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6147,13 +6206,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380933</t>
+          <t>https://artportalen.se/Sighting/126380928</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126380934</v>
+        <v>126380929</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6192,10 +6251,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>784514</v>
+        <v>784458</v>
       </c>
       <c r="R55" t="n">
-        <v>7350048</v>
+        <v>7349938</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6253,13 +6312,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380934</t>
+          <t>https://artportalen.se/Sighting/126380929</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126380935</v>
+        <v>126380930</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -6289,7 +6348,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6298,10 +6357,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>784683</v>
+        <v>784469</v>
       </c>
       <c r="R56" t="n">
-        <v>7349798</v>
+        <v>7349942</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6359,38 +6418,38 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126380935</t>
+          <t>https://artportalen.se/Sighting/126380930</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126381208</v>
+        <v>126380932</v>
       </c>
       <c r="B57" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6404,10 +6463,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>784331</v>
+        <v>784515</v>
       </c>
       <c r="R57" t="n">
-        <v>7350097</v>
+        <v>7349962</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6465,38 +6524,38 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126381208</t>
+          <t>https://artportalen.se/Sighting/126380932</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126381210</v>
+        <v>126380933</v>
       </c>
       <c r="B58" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6510,10 +6569,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>784340</v>
+        <v>784515</v>
       </c>
       <c r="R58" t="n">
-        <v>7350119</v>
+        <v>7350041</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6570,6 +6629,430 @@
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126380933</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126380934</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>784514</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7350048</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126380934</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126380935</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>784683</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7349798</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126380935</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126381208</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>784331</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7350097</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126381208</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126381210</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>784340</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7350119</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126381210</t>
         </is>
@@ -6634,6 +7117,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33409-2026 artfynd.xlsx
+++ b/artfynd/A 33409-2026 artfynd.xlsx
@@ -3131,7 +3131,7 @@
         <v>136933815</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>136933817</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136933818</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136933819</v>
       </c>
       <c r="B30" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 33409-2026 artfynd.xlsx
+++ b/artfynd/A 33409-2026 artfynd.xlsx
@@ -3131,7 +3131,7 @@
         <v>136933815</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>136933817</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136933818</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136933819</v>
       </c>
       <c r="B30" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 33409-2026 artfynd.xlsx
+++ b/artfynd/A 33409-2026 artfynd.xlsx
@@ -3157,11 +3157,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sandträsket, Nb</t>
@@ -3279,11 +3275,7 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sandträsket, Nb</t>
@@ -3401,11 +3393,7 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sandträsket, Nb</t>
@@ -3625,11 +3613,7 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sandträsket, Nb</t>

--- a/artfynd/A 33409-2026 artfynd.xlsx
+++ b/artfynd/A 33409-2026 artfynd.xlsx
@@ -3131,7 +3131,7 @@
         <v>136933815</v>
       </c>
       <c r="B26" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136933817</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>136933818</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>136933819</v>
       </c>
       <c r="B30" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 33409-2026 artfynd.xlsx
+++ b/artfynd/A 33409-2026 artfynd.xlsx
@@ -3131,7 +3131,7 @@
         <v>136933815</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136933817</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>136933818</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>136933819</v>
       </c>
       <c r="B30" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 33409-2026 artfynd.xlsx
+++ b/artfynd/A 33409-2026 artfynd.xlsx
@@ -3131,7 +3131,7 @@
         <v>136933815</v>
       </c>
       <c r="B26" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136933817</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>136933818</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>136933819</v>
       </c>
       <c r="B30" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 33409-2026 artfynd.xlsx
+++ b/artfynd/A 33409-2026 artfynd.xlsx
@@ -3131,7 +3131,7 @@
         <v>136933815</v>
       </c>
       <c r="B26" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136933817</v>
       </c>
       <c r="B27" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>136933818</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>136933819</v>
       </c>
       <c r="B30" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
